--- a/CLEANED_RESULT.xlsx
+++ b/CLEANED_RESULT.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H445"/>
+  <dimension ref="A1:H463"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16454,6 +16454,654 @@
         </is>
       </c>
     </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>Q1901</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>MUVATTUPUZHA ZONE</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>MUVAT. TOWN</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>Noufal V A</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>9400916174</t>
+        </is>
+      </c>
+      <c r="F446" t="n">
+        <v>55</v>
+      </c>
+      <c r="G446" t="inlineStr"/>
+      <c r="H446" t="inlineStr">
+        <is>
+          <t>ST0445</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>Q1902</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>MUVATTUPUZHA ZONE</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>MUVAT. TOWN</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>Faseela Siddhique</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>9895931326</t>
+        </is>
+      </c>
+      <c r="F447" t="n">
+        <v>48</v>
+      </c>
+      <c r="G447" t="inlineStr"/>
+      <c r="H447" t="inlineStr">
+        <is>
+          <t>ST0446</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>Q1904</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>MUVATTUPUZHA ZONE</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>MUVAT. TOWN</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>Rajeena Babu</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>9037265945</t>
+        </is>
+      </c>
+      <c r="F448" t="n">
+        <v>54</v>
+      </c>
+      <c r="G448" t="inlineStr"/>
+      <c r="H448" t="inlineStr">
+        <is>
+          <t>ST0447</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>Q1905</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>MUVATTUPUZHA ZONE</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>MUVAT. TOWN</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>Suhura Basheer</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>8606033725</t>
+        </is>
+      </c>
+      <c r="F449" t="n">
+        <v>52</v>
+      </c>
+      <c r="G449" t="inlineStr"/>
+      <c r="H449" t="inlineStr">
+        <is>
+          <t>ST0448</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>Q1906</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>MUVATTUPUZHA ZONE</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>MUVAT. TOWN</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>Fathimma Sulfikkar</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>9656583701</t>
+        </is>
+      </c>
+      <c r="F450" t="n">
+        <v>45</v>
+      </c>
+      <c r="G450" t="inlineStr"/>
+      <c r="H450" t="inlineStr">
+        <is>
+          <t>ST0449</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>Q1907</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>MUVATTUPUZHA ZONE</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>MUVAT. TOWN</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>Hajara Ummer</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>8281438770</t>
+        </is>
+      </c>
+      <c r="F451" t="n">
+        <v>47</v>
+      </c>
+      <c r="G451" t="inlineStr"/>
+      <c r="H451" t="inlineStr">
+        <is>
+          <t>ST0450</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>Q1909</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>MUVATTUPUZHA ZONE</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>MUVAT. TOWN</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>Zuhra Saidmuhammed</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>9947711514</t>
+        </is>
+      </c>
+      <c r="F452" t="n">
+        <v>66</v>
+      </c>
+      <c r="G452" t="inlineStr"/>
+      <c r="H452" t="inlineStr">
+        <is>
+          <t>ST0451</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>Q1912</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>MUVATTUPUZHA ZONE</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>MUVAT. TOWN</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>Sabeena Ashraf</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>9544763699</t>
+        </is>
+      </c>
+      <c r="F453" t="n">
+        <v>41</v>
+      </c>
+      <c r="G453" t="inlineStr"/>
+      <c r="H453" t="inlineStr">
+        <is>
+          <t>ST0452</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>Q1913</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>MUVATTUPUZHA ZONE</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>MUVAT. TOWN</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>Ashraf Chattayil</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>9447217410</t>
+        </is>
+      </c>
+      <c r="F454" t="n">
+        <v>40</v>
+      </c>
+      <c r="G454" t="inlineStr"/>
+      <c r="H454" t="inlineStr">
+        <is>
+          <t>ST0453</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>Q1914</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>MUVATTUPUZHA ZONE</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>MUVAT. TOWN</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>Shine P Ibrahim</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>9447105350</t>
+        </is>
+      </c>
+      <c r="F455" t="n">
+        <v>53</v>
+      </c>
+      <c r="G455" t="inlineStr"/>
+      <c r="H455" t="inlineStr">
+        <is>
+          <t>ST0454</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>Q1917</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>MUVATTUPUZHA ZONE</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>MUVAT. TOWN</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>Fathimma Panakkal</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>9446354544</t>
+        </is>
+      </c>
+      <c r="F456" t="n">
+        <v>63</v>
+      </c>
+      <c r="G456" t="inlineStr"/>
+      <c r="H456" t="inlineStr">
+        <is>
+          <t>ST0455</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>Q1918</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>MUVATTUPUZHA ZONE</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>MUVAT. TOWN</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>Saleena Noushad</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>7012503588</t>
+        </is>
+      </c>
+      <c r="F457" t="n">
+        <v>48</v>
+      </c>
+      <c r="G457" t="inlineStr"/>
+      <c r="H457" t="inlineStr">
+        <is>
+          <t>ST0456</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>Q1919</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>MUVATTUPUZHA ZONE</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>MUVAT. TOWN</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>Muhammed Shefin M M</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>9400815865</t>
+        </is>
+      </c>
+      <c r="F458" t="n">
+        <v>43</v>
+      </c>
+      <c r="G458" t="inlineStr"/>
+      <c r="H458" t="inlineStr">
+        <is>
+          <t>ST0457</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>Q1921</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>MUVATTUPUZHA ZONE</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>MUVAT. TOWN</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>Sinil V T</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>9349235566</t>
+        </is>
+      </c>
+      <c r="F459" t="n">
+        <v>58</v>
+      </c>
+      <c r="G459" t="inlineStr"/>
+      <c r="H459" t="inlineStr">
+        <is>
+          <t>ST0458</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>Q1922</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>MUVATTUPUZHA ZONE</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>MUVAT. TOWN</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>Illyas</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>9447319966</t>
+        </is>
+      </c>
+      <c r="F460" t="n">
+        <v>41</v>
+      </c>
+      <c r="G460" t="inlineStr"/>
+      <c r="H460" t="inlineStr">
+        <is>
+          <t>ST0459</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>Q1923</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>MUVATTUPUZHA ZONE</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>MUVAT. TOWN</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>Fahiza Ashraf</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>8547090595</t>
+        </is>
+      </c>
+      <c r="F461" t="n">
+        <v>30</v>
+      </c>
+      <c r="G461" t="inlineStr"/>
+      <c r="H461" t="inlineStr">
+        <is>
+          <t>ST0460</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>Q1924</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>MUVATTUPUZHA ZONE</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>MUVAT. TOWN</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>Sajida Rasheed</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>8547330075</t>
+        </is>
+      </c>
+      <c r="F462" t="n">
+        <v>27</v>
+      </c>
+      <c r="G462" t="inlineStr"/>
+      <c r="H462" t="inlineStr">
+        <is>
+          <t>ST0461</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>Q1925</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>MUVATTUPUZHA ZONE</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>MUVAT. TOWN</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>Athicka Ashraf</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>9961637556</t>
+        </is>
+      </c>
+      <c r="F463" t="n">
+        <v>39</v>
+      </c>
+      <c r="G463" t="inlineStr"/>
+      <c r="H463" t="inlineStr">
+        <is>
+          <t>ST0462</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
